--- a/dataCaseStudy_Cement/raw_results/oxy_only/Summary.xlsx
+++ b/dataCaseStudy_Cement/raw_results/oxy_only/Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3981,6 +3981,315 @@
       <c r="AE34" t="inlineStr">
         <is>
           <t>dataCaseStudy_Cement\raw_results\oxy_only\20260428130335_carbon_tax_250_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>77373790.94716127</v>
+      </c>
+      <c r="B35" t="n">
+        <v>14404244.23429232</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5951746.54475859</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13087903.06225255</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>27492147.29654487</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5951746.54475859</v>
+      </c>
+      <c r="H35" t="n">
+        <v>34650822.56924585</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9279074.536611961</v>
+      </c>
+      <c r="M35" t="n">
+        <v>77373790.94716127</v>
+      </c>
+      <c r="N35" t="n">
+        <v>61867.31730834728</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>61867.31730834728</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>61860.49691074691</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6.820397601012731</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.644999980926514</v>
+      </c>
+      <c r="W35" t="n">
+        <v>77373790.94715452</v>
+      </c>
+      <c r="X35" t="n">
+        <v>77373790.94716127</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6.750226020812988e-06</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>carbon_tax_150_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\oxy_only\20261007134600_carbon_tax_150_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>63225794.83079745</v>
+      </c>
+      <c r="B36" t="n">
+        <v>13228586.17399643</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5758365.764824538</v>
+      </c>
+      <c r="D36" t="n">
+        <v>23703694.55346782</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>36932280.72746425</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5758365.764824538</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7507405.219337074</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>13027743.11917158</v>
+      </c>
+      <c r="M36" t="n">
+        <v>63225794.83079745</v>
+      </c>
+      <c r="N36" t="n">
+        <v>144759.1919555884</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>144759.1919555884</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>144752.701324141</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6.49063144699852</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3.909000158309937</v>
+      </c>
+      <c r="W36" t="n">
+        <v>63225794.83079323</v>
+      </c>
+      <c r="X36" t="n">
+        <v>63225794.83079745</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>4.217028617858887e-06</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>carbon_tax_90_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\oxy_only\20261007134855_carbon_tax_90_el_price_107</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>67699093.04205674</v>
+      </c>
+      <c r="B37" t="n">
+        <v>17645374.89289459</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="D37" t="n">
+        <v>26513229.33165402</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>44158604.22454861</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6725637.346347709</v>
+      </c>
+      <c r="H37" t="n">
+        <v>15005442.70461023</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1809408.766550198</v>
+      </c>
+      <c r="M37" t="n">
+        <v>67699093.04205674</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7245.844635990999</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7245.844635990999</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7237.635066215869</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>8.209569775222583</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4.319999933242798</v>
+      </c>
+      <c r="W37" t="n">
+        <v>67699093.0420402</v>
+      </c>
+      <c r="X37" t="n">
+        <v>67699093.04205674</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.65402889251709e-05</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>carbon_tax_250_el_price_107</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>dataCaseStudy_Cement\raw_results\oxy_only\20261007135150_carbon_tax_250_el_price_107</t>
         </is>
       </c>
     </row>
